--- a/alocacao/saidas_m1_anual/resumo_custos.xlsx
+++ b/alocacao/saidas_m1_anual/resumo_custos.xlsx
@@ -422,7 +422,7 @@
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="92" customWidth="1" min="7" max="7"/>
@@ -485,11 +485,15 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Erro Execução</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>Sucesso</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>1651961.02</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>31.83</v>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\00.csv</t>
@@ -519,10 +523,10 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>3344863.27</v>
+        <v>1631784.92</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>17.76</v>
+        <v>32.68</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -553,10 +557,10 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>3655744.55</v>
+        <v>1769937.39</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>20.07</v>
+        <v>35.07</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -587,10 +591,10 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3288800.17</v>
+        <v>1608397.4</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>17.65</v>
+        <v>31.61</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -621,10 +625,10 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>3476052.07</v>
+        <v>1691970.72</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>20.15</v>
+        <v>34.71</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -655,10 +659,10 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3597292.84</v>
+        <v>1742818.55</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>20.72</v>
+        <v>40.5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -689,10 +693,10 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>3804673.93</v>
+        <v>1833876.28</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>21.99</v>
+        <v>36.05</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -719,11 +723,15 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Erro Execução</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+          <t>Sucesso</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>1678633.51</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>30.14</v>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\heu_full.csv</t>
@@ -749,11 +757,15 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Erro Execução</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+          <t>Sucesso</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>1653185.87</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>30.3</v>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas\heu_lim.csv</t>
